--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/panel_11/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.98485</v>
+        <v>17.5837</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31938</v>
+        <v>17.39437</v>
       </c>
       <c r="E2" t="n">
-        <v>17.53977</v>
+        <v>17.4505</v>
       </c>
       <c r="F2" t="n">
-        <v>45.599</v>
+        <v>44.41379</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05321</v>
+        <v>0.05226</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9412</v>
+        <v>1.86761</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.65972</v>
+        <v>17.80685</v>
       </c>
       <c r="D3" t="n">
-        <v>17.4448</v>
+        <v>17.14982</v>
       </c>
       <c r="E3" t="n">
-        <v>17.25253</v>
+        <v>17.73327</v>
       </c>
       <c r="F3" t="n">
-        <v>44.02446</v>
+        <v>43.77116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05343</v>
+        <v>0.05405</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86681</v>
+        <v>1.9323</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.78488</v>
+        <v>17.68674</v>
       </c>
       <c r="D4" t="n">
-        <v>17.44714</v>
+        <v>17.29673</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02015</v>
+        <v>17.63093</v>
       </c>
       <c r="F4" t="n">
-        <v>44.12219</v>
+        <v>44.7944</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05323</v>
+        <v>0.05336</v>
       </c>
       <c r="H4" t="n">
-        <v>1.92199</v>
+        <v>1.91372</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.59016</v>
+        <v>17.23361</v>
       </c>
       <c r="D6" t="n">
-        <v>16.88321</v>
+        <v>16.67043</v>
       </c>
       <c r="E6" t="n">
-        <v>17.33387</v>
+        <v>17.19963</v>
       </c>
       <c r="F6" t="n">
-        <v>22.84351</v>
+        <v>22.89206</v>
       </c>
       <c r="G6" t="n">
-        <v>35.98176</v>
+        <v>36.12794</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.49201</v>
+        <v>17.31202</v>
       </c>
       <c r="D7" t="n">
-        <v>16.46379</v>
+        <v>16.86274</v>
       </c>
       <c r="E7" t="n">
-        <v>16.83157</v>
+        <v>17.16</v>
       </c>
       <c r="F7" t="n">
-        <v>22.72139</v>
+        <v>22.67078</v>
       </c>
       <c r="G7" t="n">
-        <v>35.90831</v>
+        <v>36.12159</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.94352</v>
+        <v>17.49581</v>
       </c>
       <c r="D8" t="n">
-        <v>16.87183</v>
+        <v>16.73644</v>
       </c>
       <c r="E8" t="n">
-        <v>17.25249</v>
+        <v>17.19805</v>
       </c>
       <c r="F8" t="n">
-        <v>22.75706</v>
+        <v>22.85578</v>
       </c>
       <c r="G8" t="n">
-        <v>36.1168</v>
+        <v>35.20637</v>
       </c>
     </row>
   </sheetData>
